--- a/artfynd/A 4529-2026 artfynd.xlsx
+++ b/artfynd/A 4529-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2528,7 +2528,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131570158</v>
+        <v>131570163</v>
       </c>
       <c r="B20" t="n">
         <v>79254</v>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>644858</v>
+        <v>645121</v>
       </c>
       <c r="R20" t="n">
-        <v>7002048</v>
+        <v>7002120</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2629,7 +2629,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131570163</v>
+        <v>131570158</v>
       </c>
       <c r="B21" t="n">
         <v>79254</v>
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>645121</v>
+        <v>644858</v>
       </c>
       <c r="R21" t="n">
-        <v>7002120</v>
+        <v>7002048</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -4817,6 +4817,208 @@
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>131570150</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79016</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Stynäsgårdsbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>645073</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7002029</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>131570148</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79016</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Stynäsgårdsbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>645145</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7002031</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4529-2026 artfynd.xlsx
+++ b/artfynd/A 4529-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131570164</v>
       </c>
       <c r="B2" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>131570154</v>
       </c>
       <c r="B3" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>131570167</v>
       </c>
       <c r="B4" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>131570156</v>
       </c>
       <c r="B5" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>131570135</v>
       </c>
       <c r="B6" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>131570173</v>
       </c>
       <c r="B7" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>131570161</v>
       </c>
       <c r="B8" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>131570119</v>
       </c>
       <c r="B9" t="n">
-        <v>91822</v>
+        <v>91828</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>131570166</v>
       </c>
       <c r="B10" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>131570168</v>
       </c>
       <c r="B11" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>131570153</v>
       </c>
       <c r="B12" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>131570172</v>
       </c>
       <c r="B13" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>131570129</v>
       </c>
       <c r="B14" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>131570171</v>
       </c>
       <c r="B15" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>131570133</v>
       </c>
       <c r="B16" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>131570155</v>
       </c>
       <c r="B17" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>131570138</v>
       </c>
       <c r="B18" t="n">
-        <v>56464</v>
+        <v>56468</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>131570132</v>
       </c>
       <c r="B19" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>131570163</v>
       </c>
       <c r="B20" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>131570158</v>
       </c>
       <c r="B21" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>131570120</v>
       </c>
       <c r="B22" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>131570134</v>
       </c>
       <c r="B23" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>131570170</v>
       </c>
       <c r="B24" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>131570140</v>
       </c>
       <c r="B25" t="n">
-        <v>56464</v>
+        <v>56468</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>131570130</v>
       </c>
       <c r="B26" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>131570126</v>
       </c>
       <c r="B27" t="n">
-        <v>91843</v>
+        <v>91849</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>131570165</v>
       </c>
       <c r="B28" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>131570162</v>
       </c>
       <c r="B29" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>131570160</v>
       </c>
       <c r="B30" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>131570159</v>
       </c>
       <c r="B31" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>131570131</v>
       </c>
       <c r="B32" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>131570169</v>
       </c>
       <c r="B33" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>131570157</v>
       </c>
       <c r="B34" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>131570124</v>
       </c>
       <c r="B35" t="n">
-        <v>58051</v>
+        <v>58057</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>131570139</v>
       </c>
       <c r="B36" t="n">
-        <v>56464</v>
+        <v>56468</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>131570128</v>
       </c>
       <c r="B37" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>131570141</v>
       </c>
       <c r="B38" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>131570125</v>
       </c>
       <c r="B39" t="n">
-        <v>58051</v>
+        <v>58057</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>131570122</v>
       </c>
       <c r="B40" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>131570136</v>
       </c>
       <c r="B41" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>131570150</v>
       </c>
       <c r="B42" t="n">
-        <v>79016</v>
+        <v>79018</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>131570148</v>
       </c>
       <c r="B43" t="n">
-        <v>79016</v>
+        <v>79018</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 4529-2026 artfynd.xlsx
+++ b/artfynd/A 4529-2026 artfynd.xlsx
@@ -4400,7 +4400,7 @@
         <v>131570141</v>
       </c>
       <c r="B38" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 4529-2026 artfynd.xlsx
+++ b/artfynd/A 4529-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131570164</v>
       </c>
       <c r="B2" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>131570154</v>
       </c>
       <c r="B3" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>131570167</v>
       </c>
       <c r="B4" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>131570156</v>
       </c>
       <c r="B5" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>131570135</v>
       </c>
       <c r="B6" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>131570173</v>
       </c>
       <c r="B7" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>131570161</v>
       </c>
       <c r="B8" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>131570119</v>
       </c>
       <c r="B9" t="n">
-        <v>91828</v>
+        <v>91829</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>131570166</v>
       </c>
       <c r="B10" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>131570168</v>
       </c>
       <c r="B11" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>131570153</v>
       </c>
       <c r="B12" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>131570172</v>
       </c>
       <c r="B13" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>131570129</v>
       </c>
       <c r="B14" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>131570171</v>
       </c>
       <c r="B15" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>131570133</v>
       </c>
       <c r="B16" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>131570155</v>
       </c>
       <c r="B17" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>131570138</v>
       </c>
       <c r="B18" t="n">
-        <v>56468</v>
+        <v>56469</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>131570132</v>
       </c>
       <c r="B19" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>131570163</v>
       </c>
       <c r="B20" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>131570158</v>
       </c>
       <c r="B21" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>131570120</v>
       </c>
       <c r="B22" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>131570134</v>
       </c>
       <c r="B23" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>131570170</v>
       </c>
       <c r="B24" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>131570140</v>
       </c>
       <c r="B25" t="n">
-        <v>56468</v>
+        <v>56469</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>131570130</v>
       </c>
       <c r="B26" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>131570126</v>
       </c>
       <c r="B27" t="n">
-        <v>91849</v>
+        <v>91850</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>131570165</v>
       </c>
       <c r="B28" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>131570162</v>
       </c>
       <c r="B29" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>131570160</v>
       </c>
       <c r="B30" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>131570159</v>
       </c>
       <c r="B31" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>131570131</v>
       </c>
       <c r="B32" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>131570169</v>
       </c>
       <c r="B33" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>131570157</v>
       </c>
       <c r="B34" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>131570124</v>
       </c>
       <c r="B35" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>131570139</v>
       </c>
       <c r="B36" t="n">
-        <v>56468</v>
+        <v>56469</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>131570128</v>
       </c>
       <c r="B37" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>131570141</v>
       </c>
       <c r="B38" t="n">
-        <v>92127</v>
+        <v>92128</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>131570125</v>
       </c>
       <c r="B39" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>131570122</v>
       </c>
       <c r="B40" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>131570136</v>
       </c>
       <c r="B41" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>131570150</v>
       </c>
       <c r="B42" t="n">
-        <v>79018</v>
+        <v>79019</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>131570148</v>
       </c>
       <c r="B43" t="n">
-        <v>79018</v>
+        <v>79019</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 4529-2026 artfynd.xlsx
+++ b/artfynd/A 4529-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131570164</v>
       </c>
       <c r="B2" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>131570154</v>
       </c>
       <c r="B3" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>131570167</v>
       </c>
       <c r="B4" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>131570156</v>
       </c>
       <c r="B5" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>131570135</v>
       </c>
       <c r="B6" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>131570173</v>
       </c>
       <c r="B7" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>131570161</v>
       </c>
       <c r="B8" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>131570119</v>
       </c>
       <c r="B9" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>131570166</v>
       </c>
       <c r="B10" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>131570168</v>
       </c>
       <c r="B11" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>131570153</v>
       </c>
       <c r="B12" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>131570172</v>
       </c>
       <c r="B13" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>131570129</v>
       </c>
       <c r="B14" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>131570171</v>
       </c>
       <c r="B15" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>131570133</v>
       </c>
       <c r="B16" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>131570155</v>
       </c>
       <c r="B17" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>131570138</v>
       </c>
       <c r="B18" t="n">
-        <v>56469</v>
+        <v>56472</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>131570132</v>
       </c>
       <c r="B19" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>131570163</v>
       </c>
       <c r="B20" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>131570158</v>
       </c>
       <c r="B21" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>131570120</v>
       </c>
       <c r="B22" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>131570134</v>
       </c>
       <c r="B23" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>131570170</v>
       </c>
       <c r="B24" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>131570140</v>
       </c>
       <c r="B25" t="n">
-        <v>56469</v>
+        <v>56472</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>131570130</v>
       </c>
       <c r="B26" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>131570126</v>
       </c>
       <c r="B27" t="n">
-        <v>91850</v>
+        <v>91853</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>131570165</v>
       </c>
       <c r="B28" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>131570162</v>
       </c>
       <c r="B29" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>131570160</v>
       </c>
       <c r="B30" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>131570159</v>
       </c>
       <c r="B31" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>131570131</v>
       </c>
       <c r="B32" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>131570169</v>
       </c>
       <c r="B33" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>131570157</v>
       </c>
       <c r="B34" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>131570124</v>
       </c>
       <c r="B35" t="n">
-        <v>58058</v>
+        <v>58061</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>131570139</v>
       </c>
       <c r="B36" t="n">
-        <v>56469</v>
+        <v>56472</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>131570128</v>
       </c>
       <c r="B37" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>131570141</v>
       </c>
       <c r="B38" t="n">
-        <v>92128</v>
+        <v>92131</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>131570125</v>
       </c>
       <c r="B39" t="n">
-        <v>58058</v>
+        <v>58061</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>131570122</v>
       </c>
       <c r="B40" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>131570136</v>
       </c>
       <c r="B41" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>131570150</v>
       </c>
       <c r="B42" t="n">
-        <v>79019</v>
+        <v>79022</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>131570148</v>
       </c>
       <c r="B43" t="n">
-        <v>79019</v>
+        <v>79022</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
